--- a/data/output/sim_gridrnd/REL2/group_500_60/results/REL2_G6_results_summary.xlsx
+++ b/data/output/sim_gridrnd/REL2/group_500_60/results/REL2_G6_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,860 +466,981 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S04_G6_499_58_REL2</t>
+          <t>S01_G6_498_60_REL2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C2" t="n">
-        <v>58</v>
+        <v>88.95478131949592</v>
       </c>
       <c r="D2" t="n">
-        <v>85.9896219421794</v>
+        <v>60</v>
       </c>
       <c r="E2" t="n">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F2" t="n">
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>81.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>500.3747890056517</v>
-      </c>
-      <c r="J2" t="n">
-        <v>32.82489997110681</v>
-      </c>
-      <c r="K2" t="n">
-        <v>503.6635129088819</v>
-      </c>
-      <c r="L2" t="n">
-        <v>36.31438681311509</v>
-      </c>
-      <c r="M2" t="n">
-        <v>500.32345057573</v>
-      </c>
-      <c r="N2" t="n">
-        <v>39.65373034407791</v>
-      </c>
-      <c r="O2" t="n">
-        <v>504.524908100245</v>
-      </c>
-      <c r="P2" t="n">
-        <v>44.27250333117843</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>505.6360143085362</v>
-      </c>
       <c r="R2" t="n">
-        <v>59.24805264687654</v>
+        <v>506.21</v>
       </c>
       <c r="S2" t="n">
-        <v>504.5774762767256</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>69.57586819223053</v>
+        <v>501.4</v>
       </c>
       <c r="U2" t="n">
-        <v>508.0745944206056</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>73.49368433795874</v>
+        <v>500.1</v>
       </c>
       <c r="W2" t="n">
-        <v>504.8206882755979</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>79.43077205249106</v>
+        <v>502.07</v>
       </c>
       <c r="Y2" t="n">
-        <v>506.4206995059219</v>
+        <v>77.56</v>
       </c>
       <c r="Z2" t="n">
-        <v>75.72595389021733</v>
+        <v>504.07</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>74.02</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>502.89</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>69.98</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>497.82</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>70.48</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>508.93</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>72.38</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>503.98</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>71.09</v>
       </c>
       <c r="AJ2" t="n">
-        <v>499.925</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>503.2666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>502.3125</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>501.95</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>503.725</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>505.1285714285714</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>507.7375</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>508.05</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>507.665</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>68.79367249246111</v>
+        <v>507.85</v>
       </c>
       <c r="AT2" t="n">
-        <v>61.98248856644019</v>
+        <v>503.4833333333333</v>
       </c>
       <c r="AU2" t="n">
-        <v>58.46913582181628</v>
+        <v>501.85</v>
       </c>
       <c r="AV2" t="n">
-        <v>56.38924986200827</v>
+        <v>499.25</v>
       </c>
       <c r="AW2" t="n">
-        <v>58.60787240920227</v>
+        <v>498.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>64.91850306974374</v>
+        <v>498.2285714285715</v>
       </c>
       <c r="AY2" t="n">
-        <v>72.61030294489895</v>
+        <v>497.0875</v>
       </c>
       <c r="AZ2" t="n">
-        <v>78.7051653676908</v>
+        <v>497.1944444444445</v>
       </c>
       <c r="BA2" t="n">
-        <v>84.69907186622532</v>
+        <v>498.935</v>
       </c>
       <c r="BB2" t="n">
-        <v>331</v>
+        <v>138.5143584614967</v>
       </c>
       <c r="BC2" t="n">
-        <v>331</v>
+        <v>126.6903694928001</v>
       </c>
       <c r="BD2" t="n">
-        <v>331</v>
+        <v>119.3649969630964</v>
       </c>
       <c r="BE2" t="n">
-        <v>331</v>
+        <v>113.6243261806203</v>
       </c>
       <c r="BF2" t="n">
-        <v>331</v>
+        <v>108.5987722459758</v>
       </c>
       <c r="BG2" t="n">
-        <v>331</v>
+        <v>104.5612836609054</v>
       </c>
       <c r="BH2" t="n">
-        <v>331</v>
+        <v>100.3897023790289</v>
       </c>
       <c r="BI2" t="n">
-        <v>331</v>
+        <v>96.74474417089208</v>
       </c>
       <c r="BJ2" t="n">
-        <v>331</v>
+        <v>93.80863912774771</v>
       </c>
       <c r="BK2" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BL2" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BM2" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BN2" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BO2" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BP2" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BQ2" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BR2" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BS2" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BT2" t="n">
+        <v>705</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>705</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>705</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>705</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>705</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>705</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>705</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>705</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>705</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="CJ2" t="n">
         <v>1</v>
       </c>
-      <c r="BU2" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="BV2" t="n">
+      <c r="CK2" t="n">
         <v>0.8</v>
       </c>
-      <c r="BW2" t="n">
-        <v>0.7931034482758621</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0.9310344827586207</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.9310344827586207</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0.9310344827586207</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.9310344827586207</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>0.9310344827586207</v>
+      <c r="CL2" t="n">
+        <v>503.98</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>71.09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S01_G6_498_60_REL2</t>
+          <t>S02_G6_500_60_REL2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C3" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D3" t="n">
         <v>60</v>
       </c>
-      <c r="D3" t="n">
-        <v>88.95478131949592</v>
-      </c>
       <c r="E3" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F3" t="n">
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>506.2128616199386</v>
-      </c>
-      <c r="J3" t="n">
-        <v>79.760843429923</v>
-      </c>
-      <c r="K3" t="n">
-        <v>501.4036997685517</v>
-      </c>
-      <c r="L3" t="n">
-        <v>80.99201660422882</v>
-      </c>
-      <c r="M3" t="n">
-        <v>500.1038847547364</v>
-      </c>
-      <c r="N3" t="n">
-        <v>81.84688644178102</v>
-      </c>
-      <c r="O3" t="n">
-        <v>502.0726247346845</v>
-      </c>
-      <c r="P3" t="n">
-        <v>77.56343966479066</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>504.0650178862316</v>
-      </c>
       <c r="R3" t="n">
-        <v>74.01900305859239</v>
+        <v>494.99</v>
       </c>
       <c r="S3" t="n">
-        <v>502.8891400900764</v>
+        <v>64.08</v>
       </c>
       <c r="T3" t="n">
-        <v>69.98129975982719</v>
+        <v>487.48</v>
       </c>
       <c r="U3" t="n">
-        <v>497.8243712176727</v>
+        <v>71.36</v>
       </c>
       <c r="V3" t="n">
-        <v>70.48000598714502</v>
+        <v>488.32</v>
       </c>
       <c r="W3" t="n">
-        <v>508.9348395314074</v>
+        <v>58.19</v>
       </c>
       <c r="X3" t="n">
-        <v>72.38456505894912</v>
+        <v>481.43</v>
       </c>
       <c r="Y3" t="n">
-        <v>503.9751775395816</v>
+        <v>58.64</v>
       </c>
       <c r="Z3" t="n">
-        <v>71.08710467582507</v>
+        <v>482.51</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>57.34</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>486.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>62.97</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>487.74</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>59.93</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>493.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>491.42</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>64.75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>507.85</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>503.4833333333333</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>501.85</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>499.25</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>498.3</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>498.2285714285715</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>497.0875</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>497.1944444444445</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>498.935</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>138.5143584614967</v>
+        <v>494.65</v>
       </c>
       <c r="AT3" t="n">
-        <v>126.6903694928001</v>
+        <v>494</v>
       </c>
       <c r="AU3" t="n">
-        <v>119.3649969630964</v>
+        <v>493.2375</v>
       </c>
       <c r="AV3" t="n">
-        <v>113.6243261806203</v>
+        <v>492.61</v>
       </c>
       <c r="AW3" t="n">
-        <v>108.5987722459758</v>
+        <v>491.4833333333333</v>
       </c>
       <c r="AX3" t="n">
-        <v>104.5612836609054</v>
+        <v>491.1214285714286</v>
       </c>
       <c r="AY3" t="n">
-        <v>100.3897023790289</v>
+        <v>490.20625</v>
       </c>
       <c r="AZ3" t="n">
-        <v>96.74474417089208</v>
+        <v>491.5833333333333</v>
       </c>
       <c r="BA3" t="n">
-        <v>93.80863912774771</v>
+        <v>493.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>316</v>
+        <v>99.7623551245659</v>
       </c>
       <c r="BC3" t="n">
-        <v>316</v>
+        <v>93.78183903791465</v>
       </c>
       <c r="BD3" t="n">
-        <v>316</v>
+        <v>89.77057476562128</v>
       </c>
       <c r="BE3" t="n">
-        <v>316</v>
+        <v>85.30332877443881</v>
       </c>
       <c r="BF3" t="n">
-        <v>316</v>
+        <v>80.73371696853525</v>
       </c>
       <c r="BG3" t="n">
-        <v>316</v>
+        <v>77.00653662951912</v>
       </c>
       <c r="BH3" t="n">
-        <v>316</v>
+        <v>74.26717788456419</v>
       </c>
       <c r="BI3" t="n">
-        <v>316</v>
+        <v>71.98633165014346</v>
       </c>
       <c r="BJ3" t="n">
-        <v>316</v>
+        <v>72.46005727295555</v>
       </c>
       <c r="BK3" t="n">
-        <v>705</v>
+        <v>321</v>
       </c>
       <c r="BL3" t="n">
-        <v>705</v>
+        <v>321</v>
       </c>
       <c r="BM3" t="n">
-        <v>705</v>
+        <v>321</v>
       </c>
       <c r="BN3" t="n">
-        <v>705</v>
+        <v>321</v>
       </c>
       <c r="BO3" t="n">
-        <v>705</v>
+        <v>321</v>
       </c>
       <c r="BP3" t="n">
-        <v>705</v>
+        <v>321</v>
       </c>
       <c r="BQ3" t="n">
-        <v>705</v>
+        <v>321</v>
       </c>
       <c r="BR3" t="n">
-        <v>705</v>
+        <v>321</v>
       </c>
       <c r="BS3" t="n">
-        <v>705</v>
+        <v>321</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.625</v>
+        <v>669</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.6428571428571429</v>
+        <v>669</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.8823529411764706</v>
+        <v>669</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.8947368421052632</v>
+        <v>669</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.7916666666666666</v>
+        <v>669</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.8888888888888888</v>
+        <v>669</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.9629629629629629</v>
+        <v>669</v>
       </c>
       <c r="CA3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC3" t="n">
         <v>1</v>
       </c>
-      <c r="CB3" t="n">
-        <v>0.8</v>
+      <c r="CD3" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.8620689655172413</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>491.42</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>64.75</v>
       </c>
     </row>
     <row r="4">
@@ -1332,10 +1453,10 @@
         <v>501</v>
       </c>
       <c r="C4" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D4" t="n">
         <v>59</v>
-      </c>
-      <c r="D4" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E4" t="n">
         <v>501</v>
@@ -1344,966 +1465,1098 @@
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>529.4896111215636</v>
-      </c>
-      <c r="J4" t="n">
-        <v>50.36021161884707</v>
-      </c>
-      <c r="K4" t="n">
-        <v>525.5623531409065</v>
-      </c>
-      <c r="L4" t="n">
-        <v>54.87778650056533</v>
-      </c>
-      <c r="M4" t="n">
-        <v>525.0702919104338</v>
-      </c>
-      <c r="N4" t="n">
-        <v>61.55887901190431</v>
-      </c>
-      <c r="O4" t="n">
-        <v>525.5934765851333</v>
-      </c>
-      <c r="P4" t="n">
-        <v>60.70581009956972</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>523.6523563958082</v>
-      </c>
       <c r="R4" t="n">
-        <v>56.29814308085763</v>
+        <v>529.49</v>
       </c>
       <c r="S4" t="n">
-        <v>519.7581240612354</v>
+        <v>50.36</v>
       </c>
       <c r="T4" t="n">
-        <v>57.29006015431725</v>
+        <v>525.5599999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>516.5435362533727</v>
+        <v>54.88</v>
       </c>
       <c r="V4" t="n">
-        <v>60.58866702065294</v>
+        <v>525.0700000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>517.5067774244767</v>
+        <v>61.56</v>
       </c>
       <c r="X4" t="n">
-        <v>63.72808333676844</v>
+        <v>525.59</v>
       </c>
       <c r="Y4" t="n">
-        <v>518.936073141439</v>
+        <v>60.71</v>
       </c>
       <c r="Z4" t="n">
-        <v>62.42384040020141</v>
+        <v>523.65</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>56.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>519.76</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>57.29</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>516.54</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>60.59</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>517.51</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>63.73</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>518.9400000000001</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>62.42</v>
       </c>
       <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
         <v>510.025</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AT4" t="n">
         <v>513.1833333333333</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AU4" t="n">
         <v>515.825</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AV4" t="n">
         <v>518.11</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AW4" t="n">
         <v>517.2916666666666</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AX4" t="n">
         <v>516.5428571428571</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AY4" t="n">
         <v>513.89375</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AZ4" t="n">
         <v>511.7722222222222</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="BA4" t="n">
         <v>512.025</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="BB4" t="n">
         <v>87.99388828208468</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="BC4" t="n">
         <v>81.0774304120587</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="BD4" t="n">
         <v>76.76958626305081</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="BE4" t="n">
         <v>74.41194729342864</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="BF4" t="n">
         <v>73.05641608069449</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="BG4" t="n">
         <v>71.09142719349614</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="BH4" t="n">
         <v>70.36961319303596</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BI4" t="n">
         <v>71.47274776332239</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BJ4" t="n">
         <v>73.22871277716139</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BK4" t="n">
         <v>316</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BL4" t="n">
         <v>316</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BM4" t="n">
         <v>316</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="BN4" t="n">
         <v>316</v>
       </c>
-      <c r="BF4" t="n">
+      <c r="BO4" t="n">
         <v>316</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BP4" t="n">
         <v>316</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BQ4" t="n">
         <v>316</v>
       </c>
-      <c r="BI4" t="n">
+      <c r="BR4" t="n">
         <v>316</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BS4" t="n">
         <v>316</v>
       </c>
-      <c r="BK4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>669</v>
-      </c>
       <c r="BT4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC4" t="n">
         <v>1</v>
       </c>
-      <c r="BU4" t="n">
+      <c r="CD4" t="n">
         <v>0.7647058823529411</v>
       </c>
-      <c r="BV4" t="n">
+      <c r="CE4" t="n">
         <v>0.6296296296296297</v>
       </c>
-      <c r="BW4" t="n">
+      <c r="CF4" t="n">
         <v>0.5405405405405406</v>
       </c>
-      <c r="BX4" t="n">
+      <c r="CG4" t="n">
         <v>0.575</v>
       </c>
-      <c r="BY4" t="n">
+      <c r="CH4" t="n">
         <v>0.65</v>
       </c>
-      <c r="BZ4" t="n">
+      <c r="CI4" t="n">
         <v>0.7</v>
       </c>
-      <c r="CA4" t="n">
+      <c r="CJ4" t="n">
         <v>0.7</v>
       </c>
-      <c r="CB4" t="n">
+      <c r="CK4" t="n">
         <v>0.7</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>518.9400000000001</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>62.42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S02_G6_500_60_REL2</t>
+          <t>S04_G6_499_58_REL2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C5" t="n">
-        <v>60</v>
+        <v>85.9896219421794</v>
       </c>
       <c r="D5" t="n">
-        <v>88.95478131949592</v>
+        <v>58</v>
       </c>
       <c r="E5" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F5" t="n">
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>494.9900223958505</v>
-      </c>
-      <c r="J5" t="n">
-        <v>64.07738345883776</v>
-      </c>
-      <c r="K5" t="n">
-        <v>487.4807502140793</v>
-      </c>
-      <c r="L5" t="n">
-        <v>71.35758882524792</v>
-      </c>
-      <c r="M5" t="n">
-        <v>488.3204332560832</v>
-      </c>
-      <c r="N5" t="n">
-        <v>58.1928562953355</v>
-      </c>
-      <c r="O5" t="n">
-        <v>481.4336761775393</v>
-      </c>
-      <c r="P5" t="n">
-        <v>58.64393583990503</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>482.5089174883985</v>
-      </c>
       <c r="R5" t="n">
-        <v>57.33967475495852</v>
+        <v>500.37</v>
       </c>
       <c r="S5" t="n">
-        <v>486.1458766386029</v>
+        <v>32.82</v>
       </c>
       <c r="T5" t="n">
-        <v>62.97221060763923</v>
+        <v>503.66</v>
       </c>
       <c r="U5" t="n">
-        <v>487.7381303738241</v>
+        <v>36.31</v>
       </c>
       <c r="V5" t="n">
-        <v>59.92796588614996</v>
+        <v>500.32</v>
       </c>
       <c r="W5" t="n">
-        <v>493.1011502757079</v>
+        <v>39.65</v>
       </c>
       <c r="X5" t="n">
-        <v>65.84674075656639</v>
+        <v>504.52</v>
       </c>
       <c r="Y5" t="n">
-        <v>491.4157132870521</v>
+        <v>44.27</v>
       </c>
       <c r="Z5" t="n">
-        <v>64.7520366917411</v>
+        <v>505.64</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>59.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>504.58</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>69.58</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>508.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>504.82</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>506.42</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>75.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>494.65</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>494</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>493.2375</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>492.61</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>491.4833333333333</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>491.1214285714286</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>490.20625</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>491.5833333333333</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>493.01</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>99.7623551245659</v>
+        <v>499.925</v>
       </c>
       <c r="AT5" t="n">
-        <v>93.78183903791465</v>
+        <v>503.2666666666667</v>
       </c>
       <c r="AU5" t="n">
-        <v>89.77057476562128</v>
+        <v>502.3125</v>
       </c>
       <c r="AV5" t="n">
-        <v>85.30332877443881</v>
+        <v>501.95</v>
       </c>
       <c r="AW5" t="n">
-        <v>80.73371696853525</v>
+        <v>503.725</v>
       </c>
       <c r="AX5" t="n">
-        <v>77.00653662951912</v>
+        <v>505.1285714285714</v>
       </c>
       <c r="AY5" t="n">
-        <v>74.26717788456419</v>
+        <v>507.7375</v>
       </c>
       <c r="AZ5" t="n">
-        <v>71.98633165014346</v>
+        <v>508.05</v>
       </c>
       <c r="BA5" t="n">
-        <v>72.46005727295555</v>
+        <v>507.665</v>
       </c>
       <c r="BB5" t="n">
-        <v>321</v>
+        <v>68.79367249246111</v>
       </c>
       <c r="BC5" t="n">
-        <v>321</v>
+        <v>61.98248856644019</v>
       </c>
       <c r="BD5" t="n">
-        <v>321</v>
+        <v>58.46913582181628</v>
       </c>
       <c r="BE5" t="n">
-        <v>321</v>
+        <v>56.38924986200827</v>
       </c>
       <c r="BF5" t="n">
-        <v>321</v>
+        <v>58.60787240920227</v>
       </c>
       <c r="BG5" t="n">
-        <v>321</v>
+        <v>64.91850306974374</v>
       </c>
       <c r="BH5" t="n">
-        <v>321</v>
+        <v>72.61030294489895</v>
       </c>
       <c r="BI5" t="n">
-        <v>321</v>
+        <v>78.7051653676908</v>
       </c>
       <c r="BJ5" t="n">
-        <v>321</v>
+        <v>84.69907186622532</v>
       </c>
       <c r="BK5" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BL5" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BM5" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BN5" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BO5" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BP5" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BQ5" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BR5" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BS5" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BT5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC5" t="n">
         <v>1</v>
       </c>
-      <c r="BU5" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>0.9615384615384616</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>0.8928571428571429</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>0.8928571428571429</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0.8928571428571429</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>0.8620689655172413</v>
+      <c r="CD5" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.7931034482758621</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.9310344827586207</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.9310344827586207</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.9310344827586207</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.9310344827586207</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.9310344827586207</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>506.42</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>75.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S06_G6_502_60_REL2</t>
+          <t>S05_G6_500_60_REL2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C6" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D6" t="n">
         <v>60</v>
       </c>
-      <c r="D6" t="n">
-        <v>88.95478131949592</v>
-      </c>
       <c r="E6" t="n">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F6" t="n">
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>478.8427006292153</v>
-      </c>
-      <c r="J6" t="n">
-        <v>78.07421896409359</v>
-      </c>
-      <c r="K6" t="n">
-        <v>506.0090403308776</v>
-      </c>
-      <c r="L6" t="n">
-        <v>68.32007475966702</v>
-      </c>
-      <c r="M6" t="n">
-        <v>501.8970259279296</v>
-      </c>
-      <c r="N6" t="n">
-        <v>61.4204896227719</v>
-      </c>
-      <c r="O6" t="n">
-        <v>498.2305269820096</v>
-      </c>
-      <c r="P6" t="n">
-        <v>61.72132193940266</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>502.7458911245286</v>
-      </c>
       <c r="R6" t="n">
-        <v>56.79394370492599</v>
+        <v>510.14</v>
       </c>
       <c r="S6" t="n">
-        <v>493.9161434412904</v>
+        <v>63.47</v>
       </c>
       <c r="T6" t="n">
-        <v>60.93530812347515</v>
+        <v>512.14</v>
       </c>
       <c r="U6" t="n">
-        <v>492.2228024948736</v>
+        <v>58.79</v>
       </c>
       <c r="V6" t="n">
-        <v>64.05304380981372</v>
+        <v>515.22</v>
       </c>
       <c r="W6" t="n">
-        <v>490.3487577480878</v>
+        <v>75.73</v>
       </c>
       <c r="X6" t="n">
-        <v>66.70973813219332</v>
+        <v>515.3200000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>492.5119668170692</v>
+        <v>67.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>68.56741050007896</v>
+        <v>513.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>64.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>513.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>62.67</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>504.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>505.73</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>67.41</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>505.78</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>66.33</v>
       </c>
       <c r="AJ6" t="n">
-        <v>465.875</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>475.6166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>485.75</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>490.85</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>493.2916666666667</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>494.3642857142857</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>490.83125</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>487.2333333333333</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>486.45</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>111.5693030138667</v>
+        <v>480.175</v>
       </c>
       <c r="AT6" t="n">
-        <v>100.0656603880117</v>
+        <v>491.4833333333333</v>
       </c>
       <c r="AU6" t="n">
-        <v>91.4739717078033</v>
+        <v>500.1375</v>
       </c>
       <c r="AV6" t="n">
-        <v>85.23958880707953</v>
+        <v>503.25</v>
       </c>
       <c r="AW6" t="n">
-        <v>80.63977470137729</v>
+        <v>506.2083333333333</v>
       </c>
       <c r="AX6" t="n">
-        <v>77.13265111058311</v>
+        <v>506.7142857142857</v>
       </c>
       <c r="AY6" t="n">
-        <v>77.15521870513685</v>
+        <v>504.7625</v>
       </c>
       <c r="AZ6" t="n">
-        <v>78.19598597256909</v>
+        <v>502.6444444444444</v>
       </c>
       <c r="BA6" t="n">
-        <v>80.36627091012747</v>
+        <v>501.155</v>
       </c>
       <c r="BB6" t="n">
-        <v>288</v>
+        <v>96.1872880114623</v>
       </c>
       <c r="BC6" t="n">
-        <v>288</v>
+        <v>87.23770050207014</v>
       </c>
       <c r="BD6" t="n">
-        <v>288</v>
+        <v>85.11003814915136</v>
       </c>
       <c r="BE6" t="n">
-        <v>288</v>
+        <v>83.6374766477325</v>
       </c>
       <c r="BF6" t="n">
-        <v>288</v>
+        <v>81.7334994390645</v>
       </c>
       <c r="BG6" t="n">
-        <v>288</v>
+        <v>79.59309784453546</v>
       </c>
       <c r="BH6" t="n">
-        <v>288</v>
+        <v>77.8544706086298</v>
       </c>
       <c r="BI6" t="n">
-        <v>288</v>
+        <v>78.55214985545324</v>
       </c>
       <c r="BJ6" t="n">
-        <v>288</v>
+        <v>79.2576240812201</v>
       </c>
       <c r="BK6" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BL6" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BM6" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BN6" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BO6" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BP6" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BQ6" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BR6" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BS6" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.4</v>
+        <v>669</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.3</v>
+        <v>669</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.2</v>
+        <v>669</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.325</v>
+        <v>669</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.3617021276595745</v>
+        <v>669</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.4081632653061225</v>
+        <v>669</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.4081632653061225</v>
+        <v>669</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.4081632653061225</v>
+        <v>669</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.4081632653061225</v>
+        <v>669</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>505.78</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>66.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S05_G6_500_60_REL2</t>
+          <t>S06_G6_502_60_REL2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C7" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D7" t="n">
         <v>60</v>
       </c>
-      <c r="D7" t="n">
-        <v>88.95478131949592</v>
-      </c>
       <c r="E7" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F7" t="n">
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>510.1416360149596</v>
-      </c>
-      <c r="J7" t="n">
-        <v>63.46787174036928</v>
-      </c>
-      <c r="K7" t="n">
-        <v>512.1407820053392</v>
-      </c>
-      <c r="L7" t="n">
-        <v>58.79195433298808</v>
-      </c>
-      <c r="M7" t="n">
-        <v>515.2240643475826</v>
-      </c>
-      <c r="N7" t="n">
-        <v>75.73432039652941</v>
-      </c>
-      <c r="O7" t="n">
-        <v>515.3182323578835</v>
-      </c>
-      <c r="P7" t="n">
-        <v>67.4993269905099</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>513.6001871712857</v>
-      </c>
       <c r="R7" t="n">
-        <v>64.19792327285496</v>
+        <v>478.84</v>
       </c>
       <c r="S7" t="n">
-        <v>513.0277761598905</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>62.66732404472911</v>
+        <v>506.01</v>
       </c>
       <c r="U7" t="n">
-        <v>504.1531791286613</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>64.65033206407371</v>
+        <v>501.9</v>
       </c>
       <c r="W7" t="n">
-        <v>505.7258153360742</v>
+        <v>61.42</v>
       </c>
       <c r="X7" t="n">
-        <v>67.41200601128317</v>
+        <v>498.23</v>
       </c>
       <c r="Y7" t="n">
-        <v>505.7754393130107</v>
+        <v>61.72</v>
       </c>
       <c r="Z7" t="n">
-        <v>66.32850806629231</v>
+        <v>502.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>56.79</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>493.92</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>60.94</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>492.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>64.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>490.35</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>492.51</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="AJ7" t="n">
-        <v>480.175</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>491.4833333333333</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>500.1375</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>503.25</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>506.2083333333333</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>506.7142857142857</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>504.7625</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>502.6444444444444</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>501.155</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>96.1872880114623</v>
+        <v>465.875</v>
       </c>
       <c r="AT7" t="n">
-        <v>87.23770050207014</v>
+        <v>475.6166666666667</v>
       </c>
       <c r="AU7" t="n">
-        <v>85.11003814915136</v>
+        <v>485.75</v>
       </c>
       <c r="AV7" t="n">
-        <v>83.6374766477325</v>
+        <v>490.85</v>
       </c>
       <c r="AW7" t="n">
-        <v>81.7334994390645</v>
+        <v>493.2916666666667</v>
       </c>
       <c r="AX7" t="n">
-        <v>79.59309784453546</v>
+        <v>494.3642857142857</v>
       </c>
       <c r="AY7" t="n">
-        <v>77.8544706086298</v>
+        <v>490.83125</v>
       </c>
       <c r="AZ7" t="n">
-        <v>78.55214985545324</v>
+        <v>487.2333333333333</v>
       </c>
       <c r="BA7" t="n">
-        <v>79.2576240812201</v>
+        <v>486.45</v>
       </c>
       <c r="BB7" t="n">
-        <v>327</v>
+        <v>111.5693030138667</v>
       </c>
       <c r="BC7" t="n">
-        <v>327</v>
+        <v>100.0656603880117</v>
       </c>
       <c r="BD7" t="n">
-        <v>327</v>
+        <v>91.4739717078033</v>
       </c>
       <c r="BE7" t="n">
-        <v>327</v>
+        <v>85.23958880707953</v>
       </c>
       <c r="BF7" t="n">
-        <v>327</v>
+        <v>80.63977470137729</v>
       </c>
       <c r="BG7" t="n">
-        <v>327</v>
+        <v>77.13265111058311</v>
       </c>
       <c r="BH7" t="n">
-        <v>327</v>
+        <v>77.15521870513685</v>
       </c>
       <c r="BI7" t="n">
-        <v>327</v>
+        <v>78.19598597256909</v>
       </c>
       <c r="BJ7" t="n">
-        <v>327</v>
+        <v>80.36627091012747</v>
       </c>
       <c r="BK7" t="n">
-        <v>669</v>
+        <v>288</v>
       </c>
       <c r="BL7" t="n">
-        <v>669</v>
+        <v>288</v>
       </c>
       <c r="BM7" t="n">
-        <v>669</v>
+        <v>288</v>
       </c>
       <c r="BN7" t="n">
-        <v>669</v>
+        <v>288</v>
       </c>
       <c r="BO7" t="n">
-        <v>669</v>
+        <v>288</v>
       </c>
       <c r="BP7" t="n">
-        <v>669</v>
+        <v>288</v>
       </c>
       <c r="BQ7" t="n">
-        <v>669</v>
+        <v>288</v>
       </c>
       <c r="BR7" t="n">
-        <v>669</v>
+        <v>288</v>
       </c>
       <c r="BS7" t="n">
-        <v>669</v>
+        <v>288</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.625</v>
+        <v>669</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.7272727272727273</v>
+        <v>669</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.2666666666666667</v>
+        <v>669</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.9375</v>
+        <v>669</v>
       </c>
       <c r="BX7" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.9230769230769231</v>
+        <v>669</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.9230769230769231</v>
+        <v>669</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.9230769230769231</v>
+        <v>669</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.9285714285714286</v>
+        <v>669</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.3617021276595745</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.4081632653061225</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.4081632653061225</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.4081632653061225</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.4081632653061225</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>492.51</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>68.56999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2316,10 +2569,10 @@
         <v>502</v>
       </c>
       <c r="C8" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D8" t="n">
         <v>58</v>
-      </c>
-      <c r="D8" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E8" t="n">
         <v>502</v>
@@ -2328,228 +2581,261 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>517.7011904413885</v>
-      </c>
-      <c r="J8" t="n">
-        <v>69.54686360034862</v>
-      </c>
-      <c r="K8" t="n">
-        <v>510.9829116748717</v>
-      </c>
-      <c r="L8" t="n">
-        <v>66.14070860750691</v>
-      </c>
-      <c r="M8" t="n">
-        <v>504.9141239819205</v>
-      </c>
-      <c r="N8" t="n">
-        <v>62.71263792299596</v>
-      </c>
-      <c r="O8" t="n">
-        <v>494.5906358271201</v>
-      </c>
-      <c r="P8" t="n">
-        <v>65.04348171405104</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>490.9177147789583</v>
-      </c>
       <c r="R8" t="n">
-        <v>66.33000068895481</v>
+        <v>517.7</v>
       </c>
       <c r="S8" t="n">
-        <v>496.4193835242696</v>
+        <v>69.55</v>
       </c>
       <c r="T8" t="n">
-        <v>62.33363308263864</v>
+        <v>510.98</v>
       </c>
       <c r="U8" t="n">
-        <v>494.0172976315642</v>
+        <v>66.14</v>
       </c>
       <c r="V8" t="n">
-        <v>65.93838204676325</v>
+        <v>504.91</v>
       </c>
       <c r="W8" t="n">
-        <v>495.0319470405832</v>
+        <v>62.71</v>
       </c>
       <c r="X8" t="n">
-        <v>65.94990401457153</v>
+        <v>494.59</v>
       </c>
       <c r="Y8" t="n">
-        <v>495.5088635212811</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>65.9150989798797</v>
+        <v>490.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>66.33</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>496.42</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>62.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>494.02</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>65.94</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>495.03</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>65.95</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>495.51</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>65.92</v>
       </c>
       <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
         <v>516.35</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AT8" t="n">
         <v>516.0833333333334</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AU8" t="n">
         <v>513.3125</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AV8" t="n">
         <v>511.53</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AW8" t="n">
         <v>507.8916666666667</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AX8" t="n">
         <v>504.3642857142857</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AY8" t="n">
         <v>501.375</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AZ8" t="n">
         <v>502.1333333333333</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BA8" t="n">
         <v>500.605</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BB8" t="n">
         <v>89.71860175013875</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BC8" t="n">
         <v>86.04636185736669</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BD8" t="n">
         <v>83.18842974687045</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BE8" t="n">
         <v>80.08838305272495</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BF8" t="n">
         <v>77.79179432233768</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BG8" t="n">
         <v>75.73263221117205</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BH8" t="n">
         <v>73.33738388434647</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BI8" t="n">
         <v>73.71261010769385</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BJ8" t="n">
         <v>73.9595766280473</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BK8" t="n">
         <v>338</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BL8" t="n">
         <v>338</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BM8" t="n">
         <v>338</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BN8" t="n">
         <v>338</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BO8" t="n">
         <v>338</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BP8" t="n">
         <v>338</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BQ8" t="n">
         <v>338</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BR8" t="n">
         <v>338</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BS8" t="n">
         <v>338</v>
       </c>
-      <c r="BK8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>669</v>
-      </c>
       <c r="BT8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC8" t="n">
         <v>0.7</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="CD8" t="n">
         <v>0.65</v>
       </c>
-      <c r="BV8" t="n">
+      <c r="CE8" t="n">
         <v>0.8</v>
       </c>
-      <c r="BW8" t="n">
+      <c r="CF8" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="CG8" t="n">
         <v>0.8</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CH8" t="n">
         <v>0.6451612903225806</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CI8" t="n">
         <v>0.5405405405405406</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CJ8" t="n">
         <v>0.4761904761904762</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CK8" t="n">
         <v>0.4666666666666667</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>495.51</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>65.92</v>
       </c>
     </row>
     <row r="9">
@@ -2562,10 +2848,10 @@
         <v>499</v>
       </c>
       <c r="C9" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D9" t="n">
         <v>59</v>
-      </c>
-      <c r="D9" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E9" t="n">
         <v>499</v>
@@ -2574,228 +2860,261 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>482.0501542612049</v>
-      </c>
-      <c r="J9" t="n">
-        <v>47.39942600533459</v>
-      </c>
-      <c r="K9" t="n">
-        <v>479.381407596413</v>
-      </c>
-      <c r="L9" t="n">
-        <v>50.26699647267117</v>
-      </c>
-      <c r="M9" t="n">
-        <v>492.2767414244595</v>
-      </c>
-      <c r="N9" t="n">
-        <v>53.56836632167562</v>
-      </c>
-      <c r="O9" t="n">
-        <v>488.9463578426127</v>
-      </c>
-      <c r="P9" t="n">
-        <v>62.41885574466418</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>492.8062718507703</v>
-      </c>
       <c r="R9" t="n">
-        <v>60.03937161580851</v>
+        <v>482.05</v>
       </c>
       <c r="S9" t="n">
-        <v>497.9569834985339</v>
+        <v>47.4</v>
       </c>
       <c r="T9" t="n">
-        <v>65.60843143800635</v>
+        <v>479.38</v>
       </c>
       <c r="U9" t="n">
-        <v>494.7749017434848</v>
+        <v>50.27</v>
       </c>
       <c r="V9" t="n">
-        <v>64.68416952626295</v>
+        <v>492.28</v>
       </c>
       <c r="W9" t="n">
-        <v>495.0365273955558</v>
+        <v>53.57</v>
       </c>
       <c r="X9" t="n">
-        <v>65.68568101601302</v>
+        <v>488.95</v>
       </c>
       <c r="Y9" t="n">
-        <v>494.6176134879383</v>
+        <v>62.42</v>
       </c>
       <c r="Z9" t="n">
-        <v>63.13048616270043</v>
+        <v>492.81</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>60.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>497.96</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>65.61</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>494.77</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>495.04</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>65.69</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>494.62</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>63.13</v>
       </c>
       <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
         <v>512.425</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AT9" t="n">
         <v>500.0833333333333</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AU9" t="n">
         <v>497.125</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AV9" t="n">
         <v>497.35</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AW9" t="n">
         <v>497.7333333333333</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AX9" t="n">
         <v>500.1357142857143</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AY9" t="n">
         <v>500.79375</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
         <v>500.35</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BA9" t="n">
         <v>501.505</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="BB9" t="n">
         <v>103.9254269897411</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BC9" t="n">
         <v>89.7409775718738</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
         <v>81.56751421368681</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="BE9" t="n">
         <v>77.36593242506679</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="BF9" t="n">
         <v>75.91593303706995</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BG9" t="n">
         <v>76.53451235640463</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BH9" t="n">
         <v>77.68140839954886</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BI9" t="n">
         <v>77.37753585864283</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BJ9" t="n">
         <v>77.29586001203428</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BK9" t="n">
         <v>330</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BL9" t="n">
         <v>330</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BM9" t="n">
         <v>330</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BN9" t="n">
         <v>330</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BO9" t="n">
         <v>330</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BP9" t="n">
         <v>330</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BQ9" t="n">
         <v>330</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BR9" t="n">
         <v>330</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BS9" t="n">
         <v>330</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BT9" t="n">
         <v>706</v>
       </c>
-      <c r="BL9" t="n">
+      <c r="BU9" t="n">
         <v>706</v>
       </c>
-      <c r="BM9" t="n">
+      <c r="BV9" t="n">
         <v>706</v>
       </c>
-      <c r="BN9" t="n">
+      <c r="BW9" t="n">
         <v>706</v>
       </c>
-      <c r="BO9" t="n">
+      <c r="BX9" t="n">
         <v>706</v>
       </c>
-      <c r="BP9" t="n">
+      <c r="BY9" t="n">
         <v>706</v>
       </c>
-      <c r="BQ9" t="n">
+      <c r="BZ9" t="n">
         <v>706</v>
       </c>
-      <c r="BR9" t="n">
+      <c r="CA9" t="n">
         <v>706</v>
       </c>
-      <c r="BS9" t="n">
+      <c r="CB9" t="n">
         <v>706</v>
       </c>
-      <c r="BT9" t="n">
+      <c r="CC9" t="n">
         <v>0.3636363636363636</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="CD9" t="n">
         <v>0.4210526315789473</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="CE9" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="CF9" t="n">
         <v>0.4333333333333333</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="CG9" t="n">
         <v>0.3714285714285714</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="CH9" t="n">
         <v>0.3095238095238095</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="CI9" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CJ9" t="n">
         <v>0.3695652173913043</v>
       </c>
-      <c r="CB9" t="n">
+      <c r="CK9" t="n">
         <v>0.4375</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>494.62</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>63.13</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>498</v>
       </c>
       <c r="C10" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D10" t="n">
         <v>62</v>
-      </c>
-      <c r="D10" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E10" t="n">
         <v>498</v>
@@ -2820,1950 +3139,2214 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>487.736683506793</v>
-      </c>
-      <c r="J10" t="n">
-        <v>51.90501737657153</v>
-      </c>
-      <c r="K10" t="n">
-        <v>489.8278399851848</v>
-      </c>
-      <c r="L10" t="n">
-        <v>53.67243718079148</v>
-      </c>
-      <c r="M10" t="n">
-        <v>488.4076166022887</v>
-      </c>
-      <c r="N10" t="n">
-        <v>62.76018331436904</v>
-      </c>
-      <c r="O10" t="n">
-        <v>488.5791545792769</v>
-      </c>
-      <c r="P10" t="n">
-        <v>56.52853273852906</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>490.5686492511203</v>
-      </c>
       <c r="R10" t="n">
-        <v>63.45759326974979</v>
+        <v>487.74</v>
       </c>
       <c r="S10" t="n">
-        <v>490.2518850867866</v>
+        <v>51.91</v>
       </c>
       <c r="T10" t="n">
-        <v>69.8256567488683</v>
+        <v>489.83</v>
       </c>
       <c r="U10" t="n">
-        <v>490.5449270137142</v>
+        <v>53.67</v>
       </c>
       <c r="V10" t="n">
-        <v>67.48231939114238</v>
+        <v>488.41</v>
       </c>
       <c r="W10" t="n">
-        <v>492.0372313992541</v>
+        <v>62.76</v>
       </c>
       <c r="X10" t="n">
-        <v>66.50202503023249</v>
+        <v>488.58</v>
       </c>
       <c r="Y10" t="n">
-        <v>492.748523468216</v>
+        <v>56.53</v>
       </c>
       <c r="Z10" t="n">
-        <v>66.25445830199864</v>
+        <v>490.57</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>63.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>490.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>69.83</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>490.54</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>67.48</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>492.04</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>66.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>492.75</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>66.25</v>
       </c>
       <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
         <v>495.5</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>494.5833333333333</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>491.9625</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>491.27</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>490.3</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>489.9642857142857</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>490.1875</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>491.6666666666667</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>492.365</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>81.5732799389604</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>74.88931647586472</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>73.44308063902277</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>71.45416083056325</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>70.62324924083664</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>71.8545565424933</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>75.20074696271308</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>75.66953004861189</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>75.51173269764111</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>319</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>319</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>319</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>319</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>319</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>319</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>319</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>319</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>319</v>
       </c>
-      <c r="BK10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>669</v>
-      </c>
       <c r="BT10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC10" t="n">
         <v>1</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.7619047619047619</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.6451612903225806</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.6097560975609756</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0.5686274509803921</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>0.5535714285714286</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>0.5535714285714286</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.5892857142857143</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0.625</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>492.75</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>66.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S11_G6_500_61_REL2</t>
+          <t>S10_G6_501_58_REL2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C11" t="n">
-        <v>61</v>
+        <v>85.9896219421794</v>
       </c>
       <c r="D11" t="n">
-        <v>90.43736100815418</v>
+        <v>58</v>
       </c>
       <c r="E11" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F11" t="n">
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>503.9673613741748</v>
-      </c>
-      <c r="J11" t="n">
-        <v>64.18986011684139</v>
-      </c>
-      <c r="K11" t="n">
-        <v>479.1598853343373</v>
-      </c>
-      <c r="L11" t="n">
-        <v>57.42857128313615</v>
-      </c>
-      <c r="M11" t="n">
-        <v>497.2284078734103</v>
-      </c>
-      <c r="N11" t="n">
-        <v>60.31399177836958</v>
-      </c>
-      <c r="O11" t="n">
-        <v>509.2224987173298</v>
-      </c>
-      <c r="P11" t="n">
-        <v>57.44611383960661</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>511.0742556865122</v>
-      </c>
       <c r="R11" t="n">
-        <v>59.32373531014888</v>
+        <v>508.21</v>
       </c>
       <c r="S11" t="n">
-        <v>508.7190481351063</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>57.27370256512761</v>
+        <v>507.85</v>
       </c>
       <c r="U11" t="n">
-        <v>501.183860312396</v>
+        <v>75.59</v>
       </c>
       <c r="V11" t="n">
-        <v>58.53911046977299</v>
+        <v>509.65</v>
       </c>
       <c r="W11" t="n">
-        <v>501.0985152422047</v>
+        <v>60.87</v>
       </c>
       <c r="X11" t="n">
-        <v>59.83876112214364</v>
+        <v>514.13</v>
       </c>
       <c r="Y11" t="n">
-        <v>495.8695312512463</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="Z11" t="n">
-        <v>62.58505766017748</v>
+        <v>514.5599999999999</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>66.27</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>518.84</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>63.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>516.8</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>66.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>514.73</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>511.8</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>71.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>492.05</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>493.2333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>492.725</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>494.76</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>496.4166666666667</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>498.4428571428571</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>498.4375</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>497.2555555555555</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>495.51</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>109.1508016461629</v>
+        <v>494.825</v>
       </c>
       <c r="AT11" t="n">
-        <v>97.00882548625265</v>
+        <v>498.9666666666666</v>
       </c>
       <c r="AU11" t="n">
-        <v>89.55235549665905</v>
+        <v>502</v>
       </c>
       <c r="AV11" t="n">
-        <v>85.14013389700536</v>
+        <v>504.35</v>
       </c>
       <c r="AW11" t="n">
-        <v>81.87699955149526</v>
+        <v>506.1833333333333</v>
       </c>
       <c r="AX11" t="n">
-        <v>79.74667672686802</v>
+        <v>506.9214285714286</v>
       </c>
       <c r="AY11" t="n">
-        <v>76.69417248885341</v>
+        <v>506.3625</v>
       </c>
       <c r="AZ11" t="n">
-        <v>74.21972800200334</v>
+        <v>507.3388888888889</v>
       </c>
       <c r="BA11" t="n">
-        <v>74.08312830867769</v>
+        <v>506.565</v>
       </c>
       <c r="BB11" t="n">
-        <v>326</v>
+        <v>105.6127093440936</v>
       </c>
       <c r="BC11" t="n">
-        <v>326</v>
+        <v>99.03399528556962</v>
       </c>
       <c r="BD11" t="n">
-        <v>326</v>
+        <v>93.14343777207282</v>
       </c>
       <c r="BE11" t="n">
-        <v>326</v>
+        <v>89.04362694769345</v>
       </c>
       <c r="BF11" t="n">
-        <v>326</v>
+        <v>85.05262913174538</v>
       </c>
       <c r="BG11" t="n">
-        <v>326</v>
+        <v>81.25146749067217</v>
       </c>
       <c r="BH11" t="n">
-        <v>326</v>
+        <v>80.91411245110459</v>
       </c>
       <c r="BI11" t="n">
-        <v>326</v>
+        <v>82.14500484501571</v>
       </c>
       <c r="BJ11" t="n">
-        <v>326</v>
+        <v>83.49578297734563</v>
       </c>
       <c r="BK11" t="n">
-        <v>669</v>
+        <v>318</v>
       </c>
       <c r="BL11" t="n">
-        <v>669</v>
+        <v>318</v>
       </c>
       <c r="BM11" t="n">
-        <v>669</v>
+        <v>318</v>
       </c>
       <c r="BN11" t="n">
-        <v>669</v>
+        <v>318</v>
       </c>
       <c r="BO11" t="n">
-        <v>669</v>
+        <v>318</v>
       </c>
       <c r="BP11" t="n">
-        <v>669</v>
+        <v>318</v>
       </c>
       <c r="BQ11" t="n">
-        <v>669</v>
+        <v>318</v>
       </c>
       <c r="BR11" t="n">
-        <v>669</v>
+        <v>318</v>
       </c>
       <c r="BS11" t="n">
-        <v>669</v>
+        <v>318</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.25</v>
+        <v>669</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.8</v>
+        <v>669</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.9166666666666666</v>
+        <v>669</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.9444444444444444</v>
+        <v>669</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.92</v>
+        <v>669</v>
       </c>
       <c r="BY11" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.8571428571428571</v>
+        <v>669</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.8333333333333334</v>
+        <v>669</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.7894736842105263</v>
+        <v>669</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.4814814814814815</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.4848484848484849</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.5588235294117647</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>511.8</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>71.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S12_G6_498_60_REL2</t>
+          <t>S11_G6_500_61_REL2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C12" t="n">
-        <v>60</v>
+        <v>90.43736100815418</v>
       </c>
       <c r="D12" t="n">
-        <v>88.95478131949592</v>
+        <v>61</v>
       </c>
       <c r="E12" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F12" t="n">
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>507.9396524014424</v>
-      </c>
-      <c r="J12" t="n">
-        <v>82.10141382697428</v>
-      </c>
-      <c r="K12" t="n">
-        <v>512.2460511529192</v>
-      </c>
-      <c r="L12" t="n">
-        <v>72.17024740931325</v>
-      </c>
-      <c r="M12" t="n">
-        <v>508.5535319535135</v>
-      </c>
-      <c r="N12" t="n">
-        <v>77.20814141019422</v>
-      </c>
-      <c r="O12" t="n">
-        <v>500.2684632507981</v>
-      </c>
-      <c r="P12" t="n">
-        <v>69.10855475535146</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>502.4725691546877</v>
-      </c>
       <c r="R12" t="n">
-        <v>68.87917307007946</v>
+        <v>503.97</v>
       </c>
       <c r="S12" t="n">
-        <v>501.0752543078062</v>
+        <v>64.19</v>
       </c>
       <c r="T12" t="n">
-        <v>72.10326706408792</v>
+        <v>479.16</v>
       </c>
       <c r="U12" t="n">
-        <v>501.1398736413316</v>
+        <v>57.43</v>
       </c>
       <c r="V12" t="n">
-        <v>79.1544528123749</v>
+        <v>497.23</v>
       </c>
       <c r="W12" t="n">
-        <v>504.6303511422338</v>
+        <v>60.31</v>
       </c>
       <c r="X12" t="n">
-        <v>75.6705404558887</v>
+        <v>509.22</v>
       </c>
       <c r="Y12" t="n">
-        <v>502.109353582859</v>
+        <v>57.45</v>
       </c>
       <c r="Z12" t="n">
-        <v>82.73136289787384</v>
+        <v>511.07</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>59.32</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>508.72</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>57.27</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>501.18</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>58.54</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>501.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>59.84</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>495.87</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>62.59</v>
       </c>
       <c r="AJ12" t="n">
-        <v>507.675</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>505.8</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>508.1875</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>507.04</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>505.3833333333333</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>503.7857142857143</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>503.6</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>502.8611111111111</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>502.075</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>87.35227172203365</v>
+        <v>492.05</v>
       </c>
       <c r="AT12" t="n">
-        <v>86.24322195589248</v>
+        <v>493.2333333333333</v>
       </c>
       <c r="AU12" t="n">
-        <v>85.03280157533327</v>
+        <v>492.725</v>
       </c>
       <c r="AV12" t="n">
-        <v>82.91066517644157</v>
+        <v>494.76</v>
       </c>
       <c r="AW12" t="n">
-        <v>80.07050885868584</v>
+        <v>496.4166666666667</v>
       </c>
       <c r="AX12" t="n">
-        <v>79.48178459013519</v>
+        <v>498.4428571428571</v>
       </c>
       <c r="AY12" t="n">
-        <v>81.98896267181334</v>
+        <v>498.4375</v>
       </c>
       <c r="AZ12" t="n">
-        <v>84.53321266348438</v>
+        <v>497.2555555555555</v>
       </c>
       <c r="BA12" t="n">
-        <v>86.41110678032078</v>
+        <v>495.51</v>
       </c>
       <c r="BB12" t="n">
+        <v>109.1508016461629</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>97.00882548625265</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>89.55235549665905</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>85.14013389700536</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>81.87699955149526</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>79.74667672686802</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>76.69417248885341</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>74.21972800200334</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>74.08312830867769</v>
+      </c>
+      <c r="BK12" t="n">
         <v>326</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>326</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>326</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>326</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>326</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>326</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>326</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>326</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>326</v>
       </c>
-      <c r="BK12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>669</v>
-      </c>
       <c r="BT12" t="n">
-        <v>0.75</v>
+        <v>669</v>
       </c>
       <c r="BU12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CH12" t="n">
         <v>1</v>
       </c>
-      <c r="BV12" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>0.6451612903225806</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB12" t="n">
-        <v>0.6666666666666666</v>
+      <c r="CI12" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>495.87</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>62.59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S10_G6_501_58_REL2</t>
+          <t>S12_G6_498_60_REL2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>88.95478131949592</v>
       </c>
       <c r="D13" t="n">
-        <v>85.9896219421794</v>
+        <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="F13" t="n">
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>508.2114445035682</v>
-      </c>
-      <c r="J13" t="n">
-        <v>73.17830761415198</v>
-      </c>
-      <c r="K13" t="n">
-        <v>507.845863992876</v>
-      </c>
-      <c r="L13" t="n">
-        <v>75.58871258730628</v>
-      </c>
-      <c r="M13" t="n">
-        <v>509.6518401730866</v>
-      </c>
-      <c r="N13" t="n">
-        <v>60.86672557485289</v>
-      </c>
-      <c r="O13" t="n">
-        <v>514.1330014683911</v>
-      </c>
-      <c r="P13" t="n">
-        <v>68.71012471180087</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>514.5598224864201</v>
-      </c>
       <c r="R13" t="n">
-        <v>66.27116588305209</v>
+        <v>507.94</v>
       </c>
       <c r="S13" t="n">
-        <v>518.8384039780088</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>63.61910096651152</v>
+        <v>512.25</v>
       </c>
       <c r="U13" t="n">
-        <v>516.8043395732882</v>
+        <v>72.17</v>
       </c>
       <c r="V13" t="n">
-        <v>66.74661704558247</v>
+        <v>508.55</v>
       </c>
       <c r="W13" t="n">
-        <v>514.7285155608098</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>73.42548719441164</v>
+        <v>500.27</v>
       </c>
       <c r="Y13" t="n">
-        <v>511.8005997115222</v>
+        <v>69.11</v>
       </c>
       <c r="Z13" t="n">
-        <v>71.79859025047925</v>
+        <v>502.47</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>68.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>501.08</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>501.14</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>504.63</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>75.67</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>502.11</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>82.73</v>
       </c>
       <c r="AJ13" t="n">
-        <v>494.825</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>498.9666666666666</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>502</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>504.35</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>506.1833333333333</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>506.9214285714286</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>506.3625</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>507.3388888888889</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>506.565</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>105.6127093440936</v>
+        <v>507.675</v>
       </c>
       <c r="AT13" t="n">
-        <v>99.03399528556962</v>
+        <v>505.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>93.14343777207282</v>
+        <v>508.1875</v>
       </c>
       <c r="AV13" t="n">
-        <v>89.04362694769345</v>
+        <v>507.04</v>
       </c>
       <c r="AW13" t="n">
-        <v>85.05262913174538</v>
+        <v>505.3833333333333</v>
       </c>
       <c r="AX13" t="n">
-        <v>81.25146749067217</v>
+        <v>503.7857142857143</v>
       </c>
       <c r="AY13" t="n">
-        <v>80.91411245110459</v>
+        <v>503.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>82.14500484501571</v>
+        <v>502.8611111111111</v>
       </c>
       <c r="BA13" t="n">
-        <v>83.49578297734563</v>
+        <v>502.075</v>
       </c>
       <c r="BB13" t="n">
-        <v>318</v>
+        <v>87.35227172203365</v>
       </c>
       <c r="BC13" t="n">
-        <v>318</v>
+        <v>86.24322195589248</v>
       </c>
       <c r="BD13" t="n">
-        <v>318</v>
+        <v>85.03280157533327</v>
       </c>
       <c r="BE13" t="n">
-        <v>318</v>
+        <v>82.91066517644157</v>
       </c>
       <c r="BF13" t="n">
-        <v>318</v>
+        <v>80.07050885868584</v>
       </c>
       <c r="BG13" t="n">
-        <v>318</v>
+        <v>79.48178459013519</v>
       </c>
       <c r="BH13" t="n">
-        <v>318</v>
+        <v>81.98896267181334</v>
       </c>
       <c r="BI13" t="n">
-        <v>318</v>
+        <v>84.53321266348438</v>
       </c>
       <c r="BJ13" t="n">
-        <v>318</v>
+        <v>86.41110678032078</v>
       </c>
       <c r="BK13" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BL13" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BM13" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BN13" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BO13" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BP13" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BQ13" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BR13" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BS13" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.4545454545454545</v>
+        <v>669</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.3809523809523809</v>
+        <v>669</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.4814814814814815</v>
+        <v>669</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.4848484848484849</v>
+        <v>669</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.5454545454545454</v>
+        <v>669</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.5454545454545454</v>
+        <v>669</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.5588235294117647</v>
+        <v>669</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.6</v>
+        <v>669</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.6388888888888888</v>
+        <v>669</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>502.11</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>82.73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S15_G6_501_60_REL2</t>
+          <t>S13_G6_499_60_REL2</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C14" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D14" t="n">
         <v>60</v>
       </c>
-      <c r="D14" t="n">
-        <v>88.95478131949592</v>
-      </c>
       <c r="E14" t="n">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F14" t="n">
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>490.3424379262601</v>
-      </c>
-      <c r="J14" t="n">
-        <v>72.11973902927556</v>
-      </c>
-      <c r="K14" t="n">
-        <v>492.7506100305782</v>
-      </c>
-      <c r="L14" t="n">
-        <v>73.56081382477214</v>
-      </c>
-      <c r="M14" t="n">
-        <v>497.9082096653281</v>
-      </c>
-      <c r="N14" t="n">
-        <v>85.63247998445493</v>
-      </c>
-      <c r="O14" t="n">
-        <v>491.8265506609415</v>
-      </c>
-      <c r="P14" t="n">
-        <v>99.5591425874795</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>494.4263813441618</v>
-      </c>
       <c r="R14" t="n">
-        <v>94.434711383536</v>
+        <v>508.71</v>
       </c>
       <c r="S14" t="n">
-        <v>495.5230337797301</v>
+        <v>57.58</v>
       </c>
       <c r="T14" t="n">
-        <v>85.95696977754257</v>
+        <v>508.26</v>
       </c>
       <c r="U14" t="n">
-        <v>504.0120941139717</v>
+        <v>59.34</v>
       </c>
       <c r="V14" t="n">
-        <v>85.24717322316137</v>
+        <v>507.46</v>
       </c>
       <c r="W14" t="n">
-        <v>504.5826889671026</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>85.16288976309229</v>
+        <v>505.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>508.7666035523231</v>
+        <v>69.75</v>
       </c>
       <c r="Z14" t="n">
-        <v>84.36560159271531</v>
+        <v>512.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>68.84</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>506.56</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>503.34</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>497.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>500.36</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>63.71</v>
       </c>
       <c r="AJ14" t="n">
-        <v>495.4</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>495.9166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>495.85</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>494.58</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>492.9416666666667</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>493.8785714285714</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>497.1625</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>500.2555555555555</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>504.455</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>103.9249248255682</v>
+        <v>508.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>97.26789324106674</v>
+        <v>507.8666666666667</v>
       </c>
       <c r="AU14" t="n">
-        <v>93.0761919074905</v>
+        <v>507.1875</v>
       </c>
       <c r="AV14" t="n">
-        <v>92.90276422152357</v>
+        <v>508.21</v>
       </c>
       <c r="AW14" t="n">
-        <v>94.54569405260554</v>
+        <v>509.05</v>
       </c>
       <c r="AX14" t="n">
-        <v>93.53077933853363</v>
+        <v>508.7357142857143</v>
       </c>
       <c r="AY14" t="n">
-        <v>91.57202680813612</v>
+        <v>507.43125</v>
       </c>
       <c r="AZ14" t="n">
-        <v>90.82756080876078</v>
+        <v>505.1777777777778</v>
       </c>
       <c r="BA14" t="n">
-        <v>90.13455483331573</v>
+        <v>502.82</v>
       </c>
       <c r="BB14" t="n">
-        <v>308</v>
+        <v>94.83991775618534</v>
       </c>
       <c r="BC14" t="n">
-        <v>308</v>
+        <v>86.93378067369567</v>
       </c>
       <c r="BD14" t="n">
-        <v>308</v>
+        <v>82.91231720166793</v>
       </c>
       <c r="BE14" t="n">
-        <v>308</v>
+        <v>81.41035499247009</v>
       </c>
       <c r="BF14" t="n">
-        <v>308</v>
+        <v>79.68885848515254</v>
       </c>
       <c r="BG14" t="n">
-        <v>308</v>
+        <v>77.76205563074042</v>
       </c>
       <c r="BH14" t="n">
-        <v>308</v>
+        <v>75.31605256143939</v>
       </c>
       <c r="BI14" t="n">
-        <v>308</v>
+        <v>73.80327872538783</v>
       </c>
       <c r="BJ14" t="n">
-        <v>308</v>
+        <v>71.91034417940162</v>
       </c>
       <c r="BK14" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BL14" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BM14" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BN14" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BO14" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BP14" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BQ14" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BR14" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BS14" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.5555555555555556</v>
+        <v>669</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.5</v>
+        <v>669</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.7368421052631579</v>
+        <v>669</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.6153846153846154</v>
+        <v>669</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.4722222222222222</v>
+        <v>669</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.4186046511627907</v>
+        <v>669</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.3529411764705883</v>
+        <v>669</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.3529411764705883</v>
+        <v>669</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.3529411764705883</v>
+        <v>669</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.7659574468085106</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>500.36</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>63.71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S16_G6_502_62_REL2</t>
+          <t>S14_G6_499_61_REL2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>90.43736100815418</v>
       </c>
       <c r="D15" t="n">
-        <v>91.91994069681246</v>
+        <v>61</v>
       </c>
       <c r="E15" t="n">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="F15" t="n">
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>487.365964240687</v>
-      </c>
-      <c r="J15" t="n">
-        <v>62.47693457013095</v>
-      </c>
-      <c r="K15" t="n">
-        <v>492.9538636711966</v>
-      </c>
-      <c r="L15" t="n">
-        <v>82.13712944199206</v>
-      </c>
-      <c r="M15" t="n">
-        <v>507.608185988796</v>
-      </c>
-      <c r="N15" t="n">
-        <v>86.17466666457504</v>
-      </c>
-      <c r="O15" t="n">
-        <v>498.069850220572</v>
-      </c>
-      <c r="P15" t="n">
-        <v>86.35894809467237</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>505.344475512363</v>
-      </c>
       <c r="R15" t="n">
-        <v>84.63214459834494</v>
+        <v>553.2</v>
       </c>
       <c r="S15" t="n">
-        <v>500.9780885381657</v>
+        <v>61.19</v>
       </c>
       <c r="T15" t="n">
-        <v>81.72923590160968</v>
+        <v>541.73</v>
       </c>
       <c r="U15" t="n">
-        <v>495.6177688618316</v>
+        <v>63.01</v>
       </c>
       <c r="V15" t="n">
-        <v>80.34837985454772</v>
+        <v>525.0599999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>490.7908126817467</v>
+        <v>59.64</v>
       </c>
       <c r="X15" t="n">
-        <v>76.6519909466366</v>
+        <v>521.91</v>
       </c>
       <c r="Y15" t="n">
-        <v>492.0543517503631</v>
+        <v>60.67</v>
       </c>
       <c r="Z15" t="n">
-        <v>74.95274146128851</v>
+        <v>516.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>60.16</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>508.83</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>59.72</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>509.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>58.77</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>504.33</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>56.96</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>505.65</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>60.55</v>
       </c>
       <c r="AJ15" t="n">
-        <v>479.6</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>481.3</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>484.2125</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>487.12</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>489.7666666666667</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>493.0928571428572</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>495.45</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>494.5888888888889</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>493.865</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>91.98744479547194</v>
+        <v>533.975</v>
       </c>
       <c r="AT15" t="n">
-        <v>88.40725837471341</v>
+        <v>540.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>88.42662123902507</v>
+        <v>540.025</v>
       </c>
       <c r="AV15" t="n">
-        <v>89.18108319593344</v>
+        <v>536.95</v>
       </c>
       <c r="AW15" t="n">
-        <v>88.29786080207279</v>
+        <v>532.1833333333333</v>
       </c>
       <c r="AX15" t="n">
-        <v>87.15822200610395</v>
+        <v>528.3142857142857</v>
       </c>
       <c r="AY15" t="n">
-        <v>84.90073615699689</v>
+        <v>524.925</v>
       </c>
       <c r="AZ15" t="n">
-        <v>82.39503685760103</v>
+        <v>523.3277777777778</v>
       </c>
       <c r="BA15" t="n">
-        <v>81.1353608175868</v>
+        <v>523.55</v>
       </c>
       <c r="BB15" t="n">
-        <v>327</v>
+        <v>93.93787508241817</v>
       </c>
       <c r="BC15" t="n">
-        <v>327</v>
+        <v>87.82668539041346</v>
       </c>
       <c r="BD15" t="n">
-        <v>327</v>
+        <v>81.99130670382074</v>
       </c>
       <c r="BE15" t="n">
-        <v>327</v>
+        <v>77.96952930472263</v>
       </c>
       <c r="BF15" t="n">
-        <v>327</v>
+        <v>74.90860913287753</v>
       </c>
       <c r="BG15" t="n">
-        <v>327</v>
+        <v>72.38627392718335</v>
       </c>
       <c r="BH15" t="n">
-        <v>327</v>
+        <v>70.03209532064567</v>
       </c>
       <c r="BI15" t="n">
-        <v>327</v>
+        <v>69.32763041894749</v>
       </c>
       <c r="BJ15" t="n">
-        <v>327</v>
+        <v>70.83006070871322</v>
       </c>
       <c r="BK15" t="n">
-        <v>669</v>
+        <v>318</v>
       </c>
       <c r="BL15" t="n">
-        <v>669</v>
+        <v>318</v>
       </c>
       <c r="BM15" t="n">
-        <v>669</v>
+        <v>318</v>
       </c>
       <c r="BN15" t="n">
-        <v>669</v>
+        <v>318</v>
       </c>
       <c r="BO15" t="n">
-        <v>669</v>
+        <v>318</v>
       </c>
       <c r="BP15" t="n">
-        <v>669</v>
+        <v>318</v>
       </c>
       <c r="BQ15" t="n">
-        <v>669</v>
+        <v>318</v>
       </c>
       <c r="BR15" t="n">
-        <v>669</v>
+        <v>318</v>
       </c>
       <c r="BS15" t="n">
-        <v>669</v>
+        <v>318</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.875</v>
+        <v>675</v>
       </c>
       <c r="BU15" t="n">
-        <v>1</v>
+        <v>675</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.6363636363636364</v>
+        <v>675</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.5</v>
+        <v>675</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>675</v>
       </c>
       <c r="BY15" t="n">
+        <v>675</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>675</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>675</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>675</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.5217391304347826</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CJ15" t="n">
         <v>0.7</v>
       </c>
-      <c r="BZ15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="CB15" t="n">
-        <v>0.8</v>
+      <c r="CK15" t="n">
+        <v>0.5945945945945946</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>505.65</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>60.55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S13_G6_499_60_REL2</t>
+          <t>S15_G6_501_60_REL2</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C16" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D16" t="n">
         <v>60</v>
       </c>
-      <c r="D16" t="n">
-        <v>88.95478131949592</v>
-      </c>
       <c r="E16" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F16" t="n">
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>508.7116240684828</v>
-      </c>
-      <c r="J16" t="n">
-        <v>57.58451888653999</v>
-      </c>
-      <c r="K16" t="n">
-        <v>508.2617600334519</v>
-      </c>
-      <c r="L16" t="n">
-        <v>59.34058409083116</v>
-      </c>
-      <c r="M16" t="n">
-        <v>507.4555418767777</v>
-      </c>
-      <c r="N16" t="n">
-        <v>66.65028349686608</v>
-      </c>
-      <c r="O16" t="n">
-        <v>505.0330588983913</v>
-      </c>
-      <c r="P16" t="n">
-        <v>69.75421666045766</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>512.1416099194687</v>
-      </c>
       <c r="R16" t="n">
-        <v>68.83594471392651</v>
+        <v>490.34</v>
       </c>
       <c r="S16" t="n">
-        <v>506.5579819576902</v>
+        <v>72.12</v>
       </c>
       <c r="T16" t="n">
-        <v>64.52334875767099</v>
+        <v>492.75</v>
       </c>
       <c r="U16" t="n">
-        <v>503.3382619490576</v>
+        <v>73.56</v>
       </c>
       <c r="V16" t="n">
-        <v>66.92925213294549</v>
+        <v>497.91</v>
       </c>
       <c r="W16" t="n">
-        <v>497.8485935766262</v>
+        <v>85.63</v>
       </c>
       <c r="X16" t="n">
-        <v>65.70657207189024</v>
+        <v>491.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>500.355992577545</v>
+        <v>99.56</v>
       </c>
       <c r="Z16" t="n">
-        <v>63.70686826093853</v>
+        <v>494.43</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>495.52</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>504.01</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>85.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>504.58</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>85.16</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>508.77</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>84.37</v>
       </c>
       <c r="AJ16" t="n">
-        <v>508.2</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>507.8666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>507.1875</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>508.21</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>509.05</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>508.7357142857143</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>507.43125</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>505.1777777777778</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>502.82</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>94.83991775618534</v>
+        <v>495.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>86.93378067369567</v>
+        <v>495.9166666666667</v>
       </c>
       <c r="AU16" t="n">
-        <v>82.91231720166793</v>
+        <v>495.85</v>
       </c>
       <c r="AV16" t="n">
-        <v>81.41035499247009</v>
+        <v>494.58</v>
       </c>
       <c r="AW16" t="n">
-        <v>79.68885848515254</v>
+        <v>492.9416666666667</v>
       </c>
       <c r="AX16" t="n">
-        <v>77.76205563074042</v>
+        <v>493.8785714285714</v>
       </c>
       <c r="AY16" t="n">
-        <v>75.31605256143939</v>
+        <v>497.1625</v>
       </c>
       <c r="AZ16" t="n">
-        <v>73.80327872538783</v>
+        <v>500.2555555555555</v>
       </c>
       <c r="BA16" t="n">
-        <v>71.91034417940162</v>
+        <v>504.455</v>
       </c>
       <c r="BB16" t="n">
-        <v>316</v>
+        <v>103.9249248255682</v>
       </c>
       <c r="BC16" t="n">
-        <v>316</v>
+        <v>97.26789324106674</v>
       </c>
       <c r="BD16" t="n">
-        <v>316</v>
+        <v>93.0761919074905</v>
       </c>
       <c r="BE16" t="n">
-        <v>316</v>
+        <v>92.90276422152357</v>
       </c>
       <c r="BF16" t="n">
-        <v>316</v>
+        <v>94.54569405260554</v>
       </c>
       <c r="BG16" t="n">
-        <v>316</v>
+        <v>93.53077933853363</v>
       </c>
       <c r="BH16" t="n">
-        <v>316</v>
+        <v>91.57202680813612</v>
       </c>
       <c r="BI16" t="n">
-        <v>316</v>
+        <v>90.82756080876078</v>
       </c>
       <c r="BJ16" t="n">
-        <v>316</v>
+        <v>90.13455483331573</v>
       </c>
       <c r="BK16" t="n">
-        <v>669</v>
+        <v>308</v>
       </c>
       <c r="BL16" t="n">
-        <v>669</v>
+        <v>308</v>
       </c>
       <c r="BM16" t="n">
-        <v>669</v>
+        <v>308</v>
       </c>
       <c r="BN16" t="n">
-        <v>669</v>
+        <v>308</v>
       </c>
       <c r="BO16" t="n">
-        <v>669</v>
+        <v>308</v>
       </c>
       <c r="BP16" t="n">
-        <v>669</v>
+        <v>308</v>
       </c>
       <c r="BQ16" t="n">
-        <v>669</v>
+        <v>308</v>
       </c>
       <c r="BR16" t="n">
-        <v>669</v>
+        <v>308</v>
       </c>
       <c r="BS16" t="n">
-        <v>669</v>
+        <v>308</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.5454545454545454</v>
+        <v>669</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.9375</v>
+        <v>669</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.88</v>
+        <v>669</v>
       </c>
       <c r="BW16" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BX16" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.9444444444444444</v>
+        <v>669</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.9473684210526315</v>
+        <v>669</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.9</v>
+        <v>669</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.7659574468085106</v>
+        <v>669</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0.4722222222222222</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0.4186046511627907</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>508.77</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>84.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S14_G6_499_61_REL2</t>
+          <t>S16_G6_502_62_REL2</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C17" t="n">
-        <v>61</v>
+        <v>91.91994069681246</v>
       </c>
       <c r="D17" t="n">
-        <v>90.43736100815418</v>
+        <v>62</v>
       </c>
       <c r="E17" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F17" t="n">
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>553.196333793588</v>
-      </c>
-      <c r="J17" t="n">
-        <v>61.19228193755335</v>
-      </c>
-      <c r="K17" t="n">
-        <v>541.7301871290524</v>
-      </c>
-      <c r="L17" t="n">
-        <v>63.00523759719722</v>
-      </c>
-      <c r="M17" t="n">
-        <v>525.0609635263512</v>
-      </c>
-      <c r="N17" t="n">
-        <v>59.63876981204969</v>
-      </c>
-      <c r="O17" t="n">
-        <v>521.9109430622919</v>
-      </c>
-      <c r="P17" t="n">
-        <v>60.67472809818238</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>516.8040558701367</v>
-      </c>
       <c r="R17" t="n">
-        <v>60.15664982717376</v>
+        <v>487.37</v>
       </c>
       <c r="S17" t="n">
-        <v>508.8275212180552</v>
+        <v>62.48</v>
       </c>
       <c r="T17" t="n">
-        <v>59.71732665136278</v>
+        <v>492.95</v>
       </c>
       <c r="U17" t="n">
-        <v>509.1906865885389</v>
+        <v>82.14</v>
       </c>
       <c r="V17" t="n">
-        <v>58.77134996009305</v>
+        <v>507.61</v>
       </c>
       <c r="W17" t="n">
-        <v>504.3321668142088</v>
+        <v>86.17</v>
       </c>
       <c r="X17" t="n">
-        <v>56.95927891173594</v>
+        <v>498.07</v>
       </c>
       <c r="Y17" t="n">
-        <v>505.6531893992305</v>
+        <v>86.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>60.55349766085315</v>
+        <v>505.34</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>84.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>500.98</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>81.73</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>495.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>490.79</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>492.05</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>74.95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>533.975</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>540.2</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>540.025</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>536.95</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>532.1833333333333</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>528.3142857142857</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>524.925</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>523.3277777777778</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>523.55</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>93.93787508241817</v>
+        <v>479.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>87.82668539041346</v>
+        <v>481.3</v>
       </c>
       <c r="AU17" t="n">
-        <v>81.99130670382074</v>
+        <v>484.2125</v>
       </c>
       <c r="AV17" t="n">
-        <v>77.96952930472263</v>
+        <v>487.12</v>
       </c>
       <c r="AW17" t="n">
-        <v>74.90860913287753</v>
+        <v>489.7666666666667</v>
       </c>
       <c r="AX17" t="n">
-        <v>72.38627392718335</v>
+        <v>493.0928571428572</v>
       </c>
       <c r="AY17" t="n">
-        <v>70.03209532064567</v>
+        <v>495.45</v>
       </c>
       <c r="AZ17" t="n">
-        <v>69.32763041894749</v>
+        <v>494.5888888888889</v>
       </c>
       <c r="BA17" t="n">
-        <v>70.83006070871322</v>
+        <v>493.865</v>
       </c>
       <c r="BB17" t="n">
-        <v>318</v>
+        <v>91.98744479547194</v>
       </c>
       <c r="BC17" t="n">
-        <v>318</v>
+        <v>88.40725837471341</v>
       </c>
       <c r="BD17" t="n">
-        <v>318</v>
+        <v>88.42662123902507</v>
       </c>
       <c r="BE17" t="n">
-        <v>318</v>
+        <v>89.18108319593344</v>
       </c>
       <c r="BF17" t="n">
-        <v>318</v>
+        <v>88.29786080207279</v>
       </c>
       <c r="BG17" t="n">
-        <v>318</v>
+        <v>87.15822200610395</v>
       </c>
       <c r="BH17" t="n">
-        <v>318</v>
+        <v>84.90073615699689</v>
       </c>
       <c r="BI17" t="n">
-        <v>318</v>
+        <v>82.39503685760103</v>
       </c>
       <c r="BJ17" t="n">
-        <v>318</v>
+        <v>81.1353608175868</v>
       </c>
       <c r="BK17" t="n">
-        <v>675</v>
+        <v>327</v>
       </c>
       <c r="BL17" t="n">
-        <v>675</v>
+        <v>327</v>
       </c>
       <c r="BM17" t="n">
-        <v>675</v>
+        <v>327</v>
       </c>
       <c r="BN17" t="n">
-        <v>675</v>
+        <v>327</v>
       </c>
       <c r="BO17" t="n">
-        <v>675</v>
+        <v>327</v>
       </c>
       <c r="BP17" t="n">
-        <v>675</v>
+        <v>327</v>
       </c>
       <c r="BQ17" t="n">
-        <v>675</v>
+        <v>327</v>
       </c>
       <c r="BR17" t="n">
-        <v>675</v>
+        <v>327</v>
       </c>
       <c r="BS17" t="n">
-        <v>675</v>
+        <v>327</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.625</v>
+        <v>669</v>
       </c>
       <c r="BU17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CI17" t="n">
         <v>0.8</v>
       </c>
-      <c r="BV17" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>0.5454545454545454</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>0.5217391304347826</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CB17" t="n">
-        <v>0.5945945945945946</v>
+      <c r="CJ17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>492.05</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>74.95</v>
       </c>
     </row>
     <row r="18">
@@ -4776,10 +5359,10 @@
         <v>498</v>
       </c>
       <c r="C18" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D18" t="n">
         <v>59</v>
-      </c>
-      <c r="D18" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E18" t="n">
         <v>498</v>
@@ -4788,228 +5371,261 @@
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>471.1677234739171</v>
-      </c>
-      <c r="J18" t="n">
-        <v>56.3438028403057</v>
-      </c>
-      <c r="K18" t="n">
-        <v>469.8263134464963</v>
-      </c>
-      <c r="L18" t="n">
-        <v>56.30245051504808</v>
-      </c>
-      <c r="M18" t="n">
-        <v>479.3123014457826</v>
-      </c>
-      <c r="N18" t="n">
-        <v>55.24673842478239</v>
-      </c>
-      <c r="O18" t="n">
-        <v>482.7432124082341</v>
-      </c>
-      <c r="P18" t="n">
-        <v>55.51718884775461</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>487.2941418316426</v>
-      </c>
       <c r="R18" t="n">
-        <v>56.20752034159619</v>
+        <v>471.17</v>
       </c>
       <c r="S18" t="n">
-        <v>485.6564231997134</v>
+        <v>56.34</v>
       </c>
       <c r="T18" t="n">
-        <v>56.41891192165703</v>
+        <v>469.83</v>
       </c>
       <c r="U18" t="n">
-        <v>482.507719348376</v>
+        <v>56.3</v>
       </c>
       <c r="V18" t="n">
-        <v>54.3903006043255</v>
+        <v>479.31</v>
       </c>
       <c r="W18" t="n">
-        <v>485.1748469699339</v>
+        <v>55.25</v>
       </c>
       <c r="X18" t="n">
-        <v>55.80660971106228</v>
+        <v>482.74</v>
       </c>
       <c r="Y18" t="n">
-        <v>486.4379212850706</v>
+        <v>55.52</v>
       </c>
       <c r="Z18" t="n">
-        <v>53.56377303700971</v>
+        <v>487.29</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>56.21</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>485.66</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>56.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>482.51</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>54.39</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>485.17</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>55.81</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>486.44</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>53.56</v>
       </c>
       <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
         <v>495.425</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AT18" t="n">
         <v>486.35</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AU18" t="n">
         <v>483.6125</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AV18" t="n">
         <v>483.11</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AW18" t="n">
         <v>484.75</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AX18" t="n">
         <v>486.9285714285714</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AY18" t="n">
         <v>486.88125</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AZ18" t="n">
         <v>485.9833333333333</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="BA18" t="n">
         <v>485.895</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="BB18" t="n">
         <v>118.4345573513069</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="BC18" t="n">
         <v>100.6655891222683</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="BD18" t="n">
         <v>91.45155736098756</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="BE18" t="n">
         <v>84.93349103857676</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="BF18" t="n">
         <v>79.764053098289</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="BG18" t="n">
         <v>76.06300422836912</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BH18" t="n">
         <v>73.73697951799694</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BI18" t="n">
         <v>72.32107999132143</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BJ18" t="n">
         <v>70.4086924676208</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BK18" t="n">
         <v>327</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BL18" t="n">
         <v>327</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BM18" t="n">
         <v>327</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BN18" t="n">
         <v>327</v>
       </c>
-      <c r="BF18" t="n">
+      <c r="BO18" t="n">
         <v>327</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BP18" t="n">
         <v>327</v>
       </c>
-      <c r="BH18" t="n">
+      <c r="BQ18" t="n">
         <v>327</v>
       </c>
-      <c r="BI18" t="n">
+      <c r="BR18" t="n">
         <v>327</v>
       </c>
-      <c r="BJ18" t="n">
+      <c r="BS18" t="n">
         <v>327</v>
       </c>
-      <c r="BK18" t="n">
+      <c r="BT18" t="n">
         <v>706</v>
       </c>
-      <c r="BL18" t="n">
+      <c r="BU18" t="n">
         <v>706</v>
       </c>
-      <c r="BM18" t="n">
+      <c r="BV18" t="n">
         <v>706</v>
       </c>
-      <c r="BN18" t="n">
+      <c r="BW18" t="n">
         <v>706</v>
       </c>
-      <c r="BO18" t="n">
+      <c r="BX18" t="n">
         <v>706</v>
       </c>
-      <c r="BP18" t="n">
+      <c r="BY18" t="n">
         <v>706</v>
       </c>
-      <c r="BQ18" t="n">
+      <c r="BZ18" t="n">
         <v>706</v>
       </c>
-      <c r="BR18" t="n">
+      <c r="CA18" t="n">
         <v>706</v>
       </c>
-      <c r="BS18" t="n">
+      <c r="CB18" t="n">
         <v>706</v>
       </c>
-      <c r="BT18" t="n">
+      <c r="CC18" t="n">
         <v>1</v>
       </c>
-      <c r="BU18" t="n">
+      <c r="CD18" t="n">
         <v>0.9</v>
       </c>
-      <c r="BV18" t="n">
+      <c r="CE18" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BW18" t="n">
+      <c r="CF18" t="n">
         <v>0.95</v>
       </c>
-      <c r="BX18" t="n">
+      <c r="CG18" t="n">
         <v>0.84</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="CH18" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BZ18" t="n">
+      <c r="CI18" t="n">
         <v>0.9310344827586207</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CJ18" t="n">
         <v>0.9393939393939394</v>
       </c>
-      <c r="CB18" t="n">
+      <c r="CK18" t="n">
         <v>0.9</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>486.44</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>53.56</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>499</v>
       </c>
       <c r="C19" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D19" t="n">
         <v>58</v>
-      </c>
-      <c r="D19" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E19" t="n">
         <v>499</v>
@@ -5034,228 +5650,261 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>83.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>491.8427731197674</v>
-      </c>
-      <c r="J19" t="n">
-        <v>103.0198932811459</v>
-      </c>
-      <c r="K19" t="n">
-        <v>495.5536401855617</v>
-      </c>
-      <c r="L19" t="n">
-        <v>101.827791781345</v>
-      </c>
-      <c r="M19" t="n">
-        <v>503.6617272420625</v>
-      </c>
-      <c r="N19" t="n">
-        <v>85.60376473191351</v>
-      </c>
-      <c r="O19" t="n">
-        <v>515.9136909301608</v>
-      </c>
-      <c r="P19" t="n">
-        <v>77.81271695165624</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>519.220202507223</v>
-      </c>
       <c r="R19" t="n">
-        <v>71.17976007825872</v>
+        <v>491.84</v>
       </c>
       <c r="S19" t="n">
-        <v>517.4960834743752</v>
+        <v>103.02</v>
       </c>
       <c r="T19" t="n">
-        <v>72.06963946758056</v>
+        <v>495.55</v>
       </c>
       <c r="U19" t="n">
-        <v>509.8259178931378</v>
+        <v>101.83</v>
       </c>
       <c r="V19" t="n">
-        <v>74.12473897730021</v>
+        <v>503.66</v>
       </c>
       <c r="W19" t="n">
-        <v>510.9071322007221</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>74.96377172521915</v>
+        <v>515.91</v>
       </c>
       <c r="Y19" t="n">
-        <v>508.6048607918304</v>
+        <v>77.81</v>
       </c>
       <c r="Z19" t="n">
-        <v>74.17611522646634</v>
+        <v>519.22</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>517.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>509.83</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>74.12</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>510.91</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>508.6</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
         <v>491</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>494.7333333333333</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>496.2875</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>499.75</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>504.4</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>507.3571428571428</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>506.125</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>503.0277777777778</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>499.73</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>127.7720626741229</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>122.3361307582061</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>116.1383005031071</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>109.6630635173028</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>103.8992621083839</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>99.55738269450234</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>97.86449496625423</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>97.93344852248477</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>97.26015165523853</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>283</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>283</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>283</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>283</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>283</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>283</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>283</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>283</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>283</v>
       </c>
-      <c r="BK19" t="n">
+      <c r="BT19" t="n">
         <v>676</v>
       </c>
-      <c r="BL19" t="n">
+      <c r="BU19" t="n">
         <v>676</v>
       </c>
-      <c r="BM19" t="n">
+      <c r="BV19" t="n">
         <v>676</v>
       </c>
-      <c r="BN19" t="n">
+      <c r="BW19" t="n">
         <v>676</v>
       </c>
-      <c r="BO19" t="n">
+      <c r="BX19" t="n">
         <v>676</v>
       </c>
-      <c r="BP19" t="n">
+      <c r="BY19" t="n">
         <v>676</v>
       </c>
-      <c r="BQ19" t="n">
+      <c r="BZ19" t="n">
         <v>676</v>
       </c>
-      <c r="BR19" t="n">
+      <c r="CA19" t="n">
         <v>676</v>
       </c>
-      <c r="BS19" t="n">
+      <c r="CB19" t="n">
         <v>676</v>
       </c>
-      <c r="BT19" t="n">
+      <c r="CC19" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.5</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.391304347826087</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>0.3962264150943396</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.4909090909090909</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.6</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>508.6</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>74.18000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>500</v>
       </c>
       <c r="C20" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D20" t="n">
         <v>58</v>
-      </c>
-      <c r="D20" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E20" t="n">
         <v>500</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>512.9380579589849</v>
-      </c>
-      <c r="J20" t="n">
-        <v>47.97973580500631</v>
-      </c>
-      <c r="K20" t="n">
-        <v>521.6830421192495</v>
-      </c>
-      <c r="L20" t="n">
-        <v>49.13222268764441</v>
-      </c>
-      <c r="M20" t="n">
-        <v>525.2951782673499</v>
-      </c>
-      <c r="N20" t="n">
-        <v>62.98135907491753</v>
-      </c>
-      <c r="O20" t="n">
-        <v>527.3628299284946</v>
-      </c>
-      <c r="P20" t="n">
-        <v>66.45441756370772</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>522.655153376294</v>
-      </c>
       <c r="R20" t="n">
-        <v>66.08710143865181</v>
+        <v>512.9400000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>516.547338791725</v>
+        <v>47.98</v>
       </c>
       <c r="T20" t="n">
-        <v>69.09870633525547</v>
+        <v>521.6799999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>510.910501560856</v>
+        <v>49.13</v>
       </c>
       <c r="V20" t="n">
-        <v>70.64160669358044</v>
+        <v>525.3</v>
       </c>
       <c r="W20" t="n">
-        <v>504.9188889083487</v>
+        <v>62.98</v>
       </c>
       <c r="X20" t="n">
-        <v>70.90325012167929</v>
+        <v>527.36</v>
       </c>
       <c r="Y20" t="n">
-        <v>504.2783341776306</v>
+        <v>66.45</v>
       </c>
       <c r="Z20" t="n">
-        <v>73.16303609013366</v>
+        <v>522.66</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>66.09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>516.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>510.91</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>70.64</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>504.92</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>504.28</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>73.16</v>
       </c>
       <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
         <v>504.025</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>506.15</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>509.9375</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>515.4</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>518</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>519.5142857142857</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>517.85</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>514.8722222222223</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>510.19</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>80.0192125367402</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>74.02833353971077</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>72.62529582555929</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>76.0282842105489</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>76.1710793761867</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>76.89654327306879</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>75.43508798960866</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>74.73925270606956</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>75.99384119782339</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>331</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>331</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>331</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>331</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>331</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>331</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>331</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>331</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>331</v>
       </c>
-      <c r="BK20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>669</v>
-      </c>
       <c r="BT20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC20" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>0.8</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0.5161290322580645</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.4571428571428571</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.4634146341463415</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.5</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.5</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>504.28</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>73.16</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>501</v>
       </c>
       <c r="C21" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D21" t="n">
         <v>58</v>
-      </c>
-      <c r="D21" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E21" t="n">
         <v>501</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>506.6439525475446</v>
-      </c>
-      <c r="J21" t="n">
-        <v>78.83918502274842</v>
-      </c>
-      <c r="K21" t="n">
-        <v>495.7331108502294</v>
-      </c>
-      <c r="L21" t="n">
-        <v>64.50456817405382</v>
-      </c>
-      <c r="M21" t="n">
-        <v>488.4816768105063</v>
-      </c>
-      <c r="N21" t="n">
-        <v>60.01545407593874</v>
-      </c>
-      <c r="O21" t="n">
-        <v>497.7328883028185</v>
-      </c>
-      <c r="P21" t="n">
-        <v>69.6820544345898</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>509.6985897443945</v>
-      </c>
       <c r="R21" t="n">
-        <v>72.50385836735627</v>
+        <v>506.64</v>
       </c>
       <c r="S21" t="n">
-        <v>505.9955155084367</v>
+        <v>78.84</v>
       </c>
       <c r="T21" t="n">
-        <v>69.29398615899328</v>
+        <v>495.73</v>
       </c>
       <c r="U21" t="n">
-        <v>504.0141490527043</v>
+        <v>64.5</v>
       </c>
       <c r="V21" t="n">
-        <v>66.52398106551804</v>
+        <v>488.48</v>
       </c>
       <c r="W21" t="n">
-        <v>495.0013103425328</v>
+        <v>60.02</v>
       </c>
       <c r="X21" t="n">
-        <v>64.42888114699397</v>
+        <v>497.73</v>
       </c>
       <c r="Y21" t="n">
-        <v>500.783767641632</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="Z21" t="n">
-        <v>63.23367990704554</v>
+        <v>509.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>504.01</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>66.52</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>495</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>500.78</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>63.23</v>
       </c>
       <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
         <v>514.625</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>508.9333333333333</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>501.1375</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>499.99</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>502.2666666666667</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>504.1357142857143</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>502.10625</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>500.6944444444445</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>500.03</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>107.9005763422976</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>101.8022374781397</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>92.22943453014337</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>86.6725440955785</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>84.15360294656962</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>82.68081576713166</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>81.74729329425838</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>80.51625765591432</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>78.51617094586312</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>326</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>326</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>326</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>326</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>326</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>326</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>326</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>326</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>326</v>
       </c>
-      <c r="BK21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>669</v>
-      </c>
       <c r="BT21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC21" t="n">
         <v>0.5</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>0.5333333333333333</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>0.4</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>0.5333333333333333</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.9375</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.7894736842105263</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>0.6818181818181818</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>0.7777777777777778</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>500.78</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>63.23</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>499.85</v>
       </c>
       <c r="C22" t="n">
+        <v>88.28762045959971</v>
+      </c>
+      <c r="D22" t="n">
         <v>59.55</v>
-      </c>
-      <c r="D22" t="n">
-        <v>88.28762045959971</v>
       </c>
       <c r="E22" t="n">
         <v>499.85</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5004999999999999</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>78.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.432</v>
+      </c>
       <c r="I22" t="n">
-        <v>502.4933487202492</v>
+        <v>2.4145</v>
       </c>
       <c r="J22" t="n">
-        <v>64.8221204548053</v>
+        <v>2.438</v>
       </c>
       <c r="K22" t="n">
-        <v>501.7098312785528</v>
+        <v>2.5005</v>
       </c>
       <c r="L22" t="n">
-        <v>64.78661397447107</v>
+        <v>2.568499999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>503.3377598802065</v>
+        <v>2.6125</v>
       </c>
       <c r="N22" t="n">
-        <v>65.88903623501776</v>
+        <v>2.628</v>
       </c>
       <c r="O22" t="n">
-        <v>503.1753290517464</v>
+        <v>2.5335</v>
       </c>
       <c r="P22" t="n">
-        <v>66.773770730393</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>505.1096138844471</v>
-      </c>
+        <v>2.4735</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>66.3117735552852</v>
+        <v>502.4930000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>503.5578740833113</v>
+        <v>64.82199999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>66.64969938595655</v>
+        <v>501.7089999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>501.2219456586632</v>
+        <v>64.7865</v>
       </c>
       <c r="V22" t="n">
-        <v>67.63577664545824</v>
+        <v>503.3374999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>500.8278778416608</v>
+        <v>65.88849999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>68.65837742899112</v>
+        <v>503.174</v>
       </c>
       <c r="Y22" t="n">
-        <v>500.9312287901381</v>
+        <v>66.773</v>
       </c>
       <c r="Z22" t="n">
-        <v>68.4507610856958</v>
+        <v>505.11</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>66.312</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>503.5599999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>66.64999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>501.2205</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>67.63500000000001</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>500.828</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>68.6585</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>500.9320000000001</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>68.45099999999999</v>
       </c>
       <c r="AJ22" t="n">
-        <v>499.9787499999999</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>500.5616666666666</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>501.1337500000001</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>499.9790000000001</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>500.561</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>501.134</v>
+      </c>
+      <c r="AV22" t="n">
         <v>501.8715</v>
       </c>
-      <c r="AN22" t="n">
-        <v>502.3783333333333</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>502.8835714285714</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>502.1603125</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>501.4005555555556</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>500.92</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>99.94852640705896</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>92.15330478051648</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>87.28684741929931</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>84.168496723573</v>
-      </c>
       <c r="AW22" t="n">
-        <v>81.80650929945791</v>
+        <v>502.378</v>
       </c>
       <c r="AX22" t="n">
-        <v>80.24701031460809</v>
+        <v>502.883</v>
       </c>
       <c r="AY22" t="n">
-        <v>79.45340195945055</v>
+        <v>502.16</v>
       </c>
       <c r="AZ22" t="n">
-        <v>79.2589145996005</v>
+        <v>501.4000000000001</v>
       </c>
       <c r="BA22" t="n">
-        <v>79.53833701225339</v>
+        <v>500.9195</v>
       </c>
       <c r="BB22" t="n">
+        <v>99.94750000000001</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>92.154</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>87.2865</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>84.1675</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>81.80650000000001</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>80.2465</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>79.45349999999999</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>79.2595</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>79.539</v>
+      </c>
+      <c r="BK22" t="n">
         <v>319.6</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>319.6</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>319.6</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>319.6</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>319.6</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>319.6</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>319.6</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>319.6</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>319.6</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>675.15</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>675.15</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>675.15</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>675.15</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>675.15</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>675.15</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>675.15</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>675.15</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>675.15</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.6682215007215008</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.7146139354711337</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.6723971097674035</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.6981917143339998</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.6629601990862242</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.6845957215615013</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.635719817869449</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.6544284471895719</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.6772652522118816</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>500.9320000000001</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>68.45099999999999</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.386969433883211</v>
       </c>
       <c r="C23" t="n">
+        <v>1.952400701291484</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.316894273021107</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.952400701291484</v>
       </c>
       <c r="E23" t="n">
         <v>1.386969433883211</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01580306432642934</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.51657508881031</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2544881343526958</v>
+      </c>
       <c r="I23" t="n">
-        <v>18.58091132516449</v>
+        <v>0.2695703208714506</v>
       </c>
       <c r="J23" t="n">
-        <v>15.61220037723399</v>
+        <v>0.2581635548496952</v>
       </c>
       <c r="K23" t="n">
-        <v>17.13122756617179</v>
+        <v>0.2334066927286498</v>
       </c>
       <c r="L23" t="n">
-        <v>14.37215423206188</v>
+        <v>0.2101947718314211</v>
       </c>
       <c r="M23" t="n">
-        <v>12.83414975802319</v>
+        <v>0.1982256821217462</v>
       </c>
       <c r="N23" t="n">
-        <v>12.31124114628015</v>
+        <v>0.182485760078914</v>
       </c>
       <c r="O23" t="n">
-        <v>13.58837853268895</v>
+        <v>0.2265362757055177</v>
       </c>
       <c r="P23" t="n">
-        <v>12.00107934614188</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>12.08637624338373</v>
-      </c>
+        <v>0.2552867324979379</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>9.795326877709661</v>
+        <v>18.58119935509236</v>
       </c>
       <c r="S23" t="n">
-        <v>10.44488123408334</v>
+        <v>15.61252284141433</v>
       </c>
       <c r="T23" t="n">
-        <v>7.697278782700881</v>
+        <v>17.13083120851807</v>
       </c>
       <c r="U23" t="n">
-        <v>9.313315713351699</v>
+        <v>14.37309814421226</v>
       </c>
       <c r="V23" t="n">
-        <v>7.879792207239673</v>
+        <v>12.83428790594287</v>
       </c>
       <c r="W23" t="n">
-        <v>8.702130356681579</v>
+        <v>12.31062924339861</v>
       </c>
       <c r="X23" t="n">
-        <v>7.425877837392934</v>
+        <v>13.58765747984081</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.184798013576209</v>
+        <v>12.00101228186496</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.566421900556612</v>
+        <v>12.08579549022648</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>9.794211824499095</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>10.44508496853903</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>7.69771052771024</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>9.31259841346797</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>7.879574861628006</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>8.702843818334081</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>7.424422199740529</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>8.184956418878935</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>7.567600537471363</v>
       </c>
       <c r="AJ23" t="n">
-        <v>15.0962052459864</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>13.83715028718615</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>12.89403236864574</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>15.09528434557243</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>13.8367458526011</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>12.89384120627486</v>
+      </c>
+      <c r="AV23" t="n">
         <v>12.29842534850018</v>
       </c>
-      <c r="AN23" t="n">
-        <v>11.36371874877099</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>10.42016091482612</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>9.633580051963989</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>9.131160706145506</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>8.804143761230899</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>16.54554242108219</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>14.96210031642388</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>13.48552289445252</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>12.26601828304007</v>
-      </c>
       <c r="AW23" t="n">
-        <v>11.0275731698457</v>
+        <v>11.36315124935813</v>
       </c>
       <c r="AX23" t="n">
-        <v>9.56081522753585</v>
+        <v>10.41964495808909</v>
       </c>
       <c r="AY23" t="n">
-        <v>8.437640171817026</v>
+        <v>9.632283983398855</v>
       </c>
       <c r="AZ23" t="n">
-        <v>8.016017489978077</v>
+        <v>9.131705322953824</v>
       </c>
       <c r="BA23" t="n">
-        <v>7.697726617590603</v>
+        <v>8.80359464560985</v>
       </c>
       <c r="BB23" t="n">
+        <v>16.54505328362211</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>14.96255058470981</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>13.48479973701384</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>12.26488177684563</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>11.02779897636686</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>9.561092909891576</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>8.436676369157155</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>8.015316571218015</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>7.697711826797693</v>
+      </c>
+      <c r="BK23" t="n">
         <v>13.597213336795</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>13.597213336795</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>13.597213336795</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>13.597213336795</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>13.597213336795</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>13.597213336795</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>13.597213336795</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>13.597213336795</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>13.597213336795</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>13.30324455873355</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>13.30324455873355</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>13.30324455873355</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>13.30324455873355</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>13.30324455873355</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>13.30324455873355</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>13.30324455873355</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>13.30324455873355</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>13.30324455873355</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.2411839268641461</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.2022695311128413</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.2110962319949104</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.2029989329741302</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.2662406448680802</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.2149196697390461</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.2891270892825529</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.2590559405061787</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.1777796228851286</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>8.184956418878935</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>7.567600537471363</v>
       </c>
     </row>
   </sheetData>
